--- a/business_surveys/023_transformation_consulting_efficiency_survey--business_surveys.xlsx
+++ b/business_surveys/023_transformation_consulting_efficiency_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>transformation_consulting_efficiency_survey_form_business_surveys</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>Transformation Consulting Efficiency Survey Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,179 +543,179 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>business_surveys_form_business_surveys</t>
+          <t>participate_in_decision_making</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>business_surveys</t>
+          <t>Do you participate in the decision-making process for business surveys?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>feedback_business_surveys</t>
+          <t>communication_methods</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>How do you currently communicate with your team regarding business surveys?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>communication_form_business_surveys</t>
+          <t>communication_areas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>Which areas of communication do you participate in during business surveys?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>communication_form_business_surveys_form_1</t>
+          <t>impact_on_business</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>Do these surveys positively impact your business?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>impact_form_business_surveys</t>
+          <t>areas_of_impact</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>What areas of business do these surveys have a positive impact on?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>impact_form_business_surveys_form_1</t>
+          <t>efficiency_value</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>How valuable is the information from business surveys for your business operations?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>value_form_business_surveys</t>
+          <t>operations_efficiency</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>In which business operations do you find the information from business surveys valuable?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>value_form_business_surveys_form_1</t>
+          <t>transformation_projects_benefit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>Do you believe business surveys help transform your business?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>transformation_projects_form_business_surveys</t>
+          <t>transformation_projects_benefiting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>transformation_projects</t>
+          <t>Which business transformation projects benefit from business surveys?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>overall_efficiency_form_business_surveys</t>
+          <t>overall_efficiency</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>overall_efficiency</t>
+          <t>What is your overall efficiency in business surveys?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>overall_efficiency_form_business_surveys_form_1</t>
+          <t>areas_for_improvement</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>overall_efficiency</t>
+          <t>In which areas do you see room for improvement in business surveys?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,306 +827,578 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>business_surveys_form_business_surveys_choices</t>
+          <t>participate_in_decision_making_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>business_surveys_form_business_surveys_choices</t>
+          <t>participate_in_decision_making_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>communication_form_business_surveys_choices</t>
+          <t>communication_methods_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>communication_form_business_surveys_choices</t>
+          <t>communication_methods_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Phone call</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>communication_form_business_surveys_form_1_choices</t>
+          <t>communication_methods_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>in-person_meeting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>In-person meeting</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>communication_form_business_surveys_form_1_choices</t>
+          <t>communication_methods_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>impact_form_business_surveys_choices</t>
+          <t>communication_areas_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>impact_form_business_surveys_choices</t>
+          <t>communication_areas_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Phone call</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>impact_form_business_surveys_form_1_choices</t>
+          <t>communication_areas_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>in-person_meeting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>In-person meeting</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>impact_form_business_surveys_form_1_choices</t>
+          <t>communication_areas_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>value_form_business_surveys_choices</t>
+          <t>impact_on_business_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>value_form_business_surveys_choices</t>
+          <t>impact_on_business_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>value_form_business_surveys_form_1_choices</t>
+          <t>areas_of_impact_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>value_form_business_surveys_form_1_choices</t>
+          <t>areas_of_impact_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>overall_efficiency_form_business_surveys_choices</t>
+          <t>areas_of_impact_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>overall_efficiency_form_business_surveys_choices</t>
+          <t>areas_of_impact_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>overall_efficiency_form_business_surveys_form_1_choices</t>
+          <t>efficiency_value_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_valuable</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very valuable</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>overall_efficiency_form_business_surveys_form_1_choices</t>
+          <t>efficiency_value_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>somewhat_valuable</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Somewhat valuable</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>efficiency_value_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>not_very_valuable</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Not very valuable</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>efficiency_value_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>not_at_all_valuable</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Not at all valuable</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>operations_efficiency_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>operations_efficiency_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>operations_efficiency_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>operations_efficiency_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>transformation_projects_benefit_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>transformation_projects_benefit_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>overall_efficiency_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>very_efficient</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Very efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>overall_efficiency_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>somewhat_efficient</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Somewhat efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>overall_efficiency_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>not_very_efficient</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Not very efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>overall_efficiency_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>not_at_all_efficient</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Not at all efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>areas_for_improvement_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>communication</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>areas_for_improvement_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>data_analysis</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Data analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>areas_for_improvement_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>feedback_mechanisms</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Feedback mechanisms</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>areas_for_improvement_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
